--- a/output/yearly_total_coral_cover_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_96_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.242908728811628</v>
+        <v>1.250379828840946</v>
       </c>
       <c r="C3" t="n">
-        <v>4.580144510439694</v>
+        <v>4.658880676320288</v>
       </c>
       <c r="D3" t="n">
-        <v>6.13932500127242</v>
+        <v>6.075295416001443</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96237824052374</v>
+        <v>11.98455592116268</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.343810577325562</v>
+        <v>1.366760030407627</v>
       </c>
       <c r="C4" t="n">
-        <v>4.995831962235985</v>
+        <v>5.212385568519474</v>
       </c>
       <c r="D4" t="n">
-        <v>6.432249745336117</v>
+        <v>6.324806828554731</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77189228489766</v>
+        <v>12.90395242748183</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.481930491425274</v>
+        <v>1.530124413507809</v>
       </c>
       <c r="C5" t="n">
-        <v>5.510588739019083</v>
+        <v>5.945004458522698</v>
       </c>
       <c r="D5" t="n">
-        <v>6.880113644185345</v>
+        <v>6.627562648923829</v>
       </c>
       <c r="E5" t="n">
-        <v>13.8726328746297</v>
+        <v>14.10269152095434</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.643095509690844</v>
+        <v>1.709492495207176</v>
       </c>
       <c r="C6" t="n">
-        <v>6.163206305216294</v>
+        <v>6.876230642371564</v>
       </c>
       <c r="D6" t="n">
-        <v>7.275173624568255</v>
+        <v>6.919491523029926</v>
       </c>
       <c r="E6" t="n">
-        <v>15.08147543947539</v>
+        <v>15.50521466060867</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.82605020877407</v>
+        <v>1.906591074338644</v>
       </c>
       <c r="C7" t="n">
-        <v>6.985418560324604</v>
+        <v>7.985701218246197</v>
       </c>
       <c r="D7" t="n">
-        <v>7.663667772986803</v>
+        <v>7.286478355303323</v>
       </c>
       <c r="E7" t="n">
-        <v>16.47513654208548</v>
+        <v>17.17877064788816</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.076608749592437</v>
+        <v>1.138919691575567</v>
       </c>
       <c r="C8" t="n">
-        <v>4.754337838902644</v>
+        <v>5.668069488386996</v>
       </c>
       <c r="D8" t="n">
-        <v>5.970472647566825</v>
+        <v>5.655301243798925</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80141923606191</v>
+        <v>12.46229042376149</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.333202316166956</v>
+        <v>1.413112089451267</v>
       </c>
       <c r="C9" t="n">
-        <v>5.947388865947047</v>
+        <v>7.065790992798131</v>
       </c>
       <c r="D9" t="n">
-        <v>6.55676662010464</v>
+        <v>6.255174195623272</v>
       </c>
       <c r="E9" t="n">
-        <v>13.83735780221864</v>
+        <v>14.73407727787267</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.598646282776355</v>
+        <v>1.688243915649621</v>
       </c>
       <c r="C10" t="n">
-        <v>7.376385138079852</v>
+        <v>8.60037027919876</v>
       </c>
       <c r="D10" t="n">
-        <v>7.225297630217931</v>
+        <v>6.809985961476492</v>
       </c>
       <c r="E10" t="n">
-        <v>16.20032905107414</v>
+        <v>17.09860015632487</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.868192257634928</v>
+        <v>1.973783709944456</v>
       </c>
       <c r="C11" t="n">
-        <v>8.948911441745581</v>
+        <v>10.24420338264728</v>
       </c>
       <c r="D11" t="n">
-        <v>7.841948483554443</v>
+        <v>7.386207890842336</v>
       </c>
       <c r="E11" t="n">
-        <v>18.65905218293495</v>
+        <v>19.60419498343408</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.131359949952992</v>
+        <v>2.258678148058155</v>
       </c>
       <c r="C12" t="n">
-        <v>10.67257971736205</v>
+        <v>11.98482855300858</v>
       </c>
       <c r="D12" t="n">
-        <v>8.381000267825279</v>
+        <v>8.002876684664541</v>
       </c>
       <c r="E12" t="n">
-        <v>21.18493993514032</v>
+        <v>22.24638338573128</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.378702443271039</v>
+        <v>2.524983298999787</v>
       </c>
       <c r="C13" t="n">
-        <v>12.42058665193157</v>
+        <v>13.72793790798241</v>
       </c>
       <c r="D13" t="n">
-        <v>8.910236692157298</v>
+        <v>8.529083963427944</v>
       </c>
       <c r="E13" t="n">
-        <v>23.70952578735991</v>
+        <v>24.78200517041014</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.376488821170368</v>
+        <v>1.457846253421301</v>
       </c>
       <c r="C14" t="n">
-        <v>8.611439257709067</v>
+        <v>9.583585469408343</v>
       </c>
       <c r="D14" t="n">
-        <v>6.737439969934585</v>
+        <v>6.530644633512036</v>
       </c>
       <c r="E14" t="n">
-        <v>16.72536804881402</v>
+        <v>17.57207635634168</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.383321785191926</v>
+        <v>1.471580903803714</v>
       </c>
       <c r="C15" t="n">
-        <v>9.500392168950469</v>
+        <v>10.37739721063119</v>
       </c>
       <c r="D15" t="n">
-        <v>6.791514633484499</v>
+        <v>6.588616835447811</v>
       </c>
       <c r="E15" t="n">
-        <v>17.67522858762689</v>
+        <v>18.43759494988271</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.584010650894059</v>
+        <v>1.686102594658685</v>
       </c>
       <c r="C16" t="n">
-        <v>11.35251811787433</v>
+        <v>12.29934505628108</v>
       </c>
       <c r="D16" t="n">
-        <v>7.299097831534187</v>
+        <v>7.073767098455458</v>
       </c>
       <c r="E16" t="n">
-        <v>20.23562660030258</v>
+        <v>21.05921474939523</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.25899325592611</v>
+        <v>1.342530168080471</v>
       </c>
       <c r="C17" t="n">
-        <v>10.63790396395308</v>
+        <v>11.33671197983596</v>
       </c>
       <c r="D17" t="n">
-        <v>6.800320910391594</v>
+        <v>6.589470955950507</v>
       </c>
       <c r="E17" t="n">
-        <v>18.69721813027078</v>
+        <v>19.26871310386694</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.416779746952657</v>
+        <v>1.51428692893845</v>
       </c>
       <c r="C18" t="n">
-        <v>12.45412739933263</v>
+        <v>13.26753482473225</v>
       </c>
       <c r="D18" t="n">
-        <v>7.251237630952154</v>
+        <v>7.080688419770398</v>
       </c>
       <c r="E18" t="n">
-        <v>21.12214477723744</v>
+        <v>21.86251017344109</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.402642580011503</v>
+        <v>1.502466686579319</v>
       </c>
       <c r="C19" t="n">
-        <v>13.36415843378422</v>
+        <v>14.20194265468028</v>
       </c>
       <c r="D19" t="n">
-        <v>7.349765830550363</v>
+        <v>7.203789764405906</v>
       </c>
       <c r="E19" t="n">
-        <v>22.11656684434608</v>
+        <v>22.9081991056655</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.537888143748544</v>
+        <v>1.651466535652857</v>
       </c>
       <c r="C20" t="n">
-        <v>15.37821384904655</v>
+        <v>16.33576147238367</v>
       </c>
       <c r="D20" t="n">
-        <v>7.794772429931359</v>
+        <v>7.695066133088052</v>
       </c>
       <c r="E20" t="n">
-        <v>24.71087442272645</v>
+        <v>25.68229414112458</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9034533248331275</v>
+        <v>0.9718026000027903</v>
       </c>
       <c r="C21" t="n">
-        <v>11.24577268999158</v>
+        <v>12.05452663127306</v>
       </c>
       <c r="D21" t="n">
-        <v>6.492582275018388</v>
+        <v>6.455069695239119</v>
       </c>
       <c r="E21" t="n">
-        <v>18.64180828984309</v>
+        <v>19.48139892651497</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_96_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250379828840946</v>
+        <v>1.294725372641775</v>
       </c>
       <c r="C3" t="n">
-        <v>4.658880676320288</v>
+        <v>4.640521994250872</v>
       </c>
       <c r="D3" t="n">
-        <v>6.075295416001443</v>
+        <v>6.041650922176904</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98455592116268</v>
+        <v>11.97689828906955</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.366760030407627</v>
+        <v>1.480958237887168</v>
       </c>
       <c r="C4" t="n">
-        <v>5.212385568519474</v>
+        <v>5.176794278670436</v>
       </c>
       <c r="D4" t="n">
-        <v>6.324806828554731</v>
+        <v>6.328822331314694</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90395242748183</v>
+        <v>12.9865748478723</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.530124413507809</v>
+        <v>1.717643692008971</v>
       </c>
       <c r="C5" t="n">
-        <v>5.945004458522698</v>
+        <v>5.873719255207845</v>
       </c>
       <c r="D5" t="n">
-        <v>6.627562648923829</v>
+        <v>6.58427440991431</v>
       </c>
       <c r="E5" t="n">
-        <v>14.10269152095434</v>
+        <v>14.17563735713113</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.709492495207176</v>
+        <v>1.972914935116205</v>
       </c>
       <c r="C6" t="n">
-        <v>6.876230642371564</v>
+        <v>6.766516756202575</v>
       </c>
       <c r="D6" t="n">
-        <v>6.919491523029926</v>
+        <v>7.01727602271855</v>
       </c>
       <c r="E6" t="n">
-        <v>15.50521466060867</v>
+        <v>15.75670771403733</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.906591074338644</v>
+        <v>2.248785523190296</v>
       </c>
       <c r="C7" t="n">
-        <v>7.985701218246197</v>
+        <v>7.83521365991368</v>
       </c>
       <c r="D7" t="n">
-        <v>7.286478355303323</v>
+        <v>7.36979156099785</v>
       </c>
       <c r="E7" t="n">
-        <v>17.17877064788816</v>
+        <v>17.45379074410183</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.138919691575567</v>
+        <v>1.4181943246907</v>
       </c>
       <c r="C8" t="n">
-        <v>5.668069488386996</v>
+        <v>5.537105621331631</v>
       </c>
       <c r="D8" t="n">
-        <v>5.655301243798925</v>
+        <v>5.639472283426862</v>
       </c>
       <c r="E8" t="n">
-        <v>12.46229042376149</v>
+        <v>12.59477222944919</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.413112089451267</v>
+        <v>1.808465363958386</v>
       </c>
       <c r="C9" t="n">
-        <v>7.065790992798131</v>
+        <v>6.854411349064364</v>
       </c>
       <c r="D9" t="n">
-        <v>6.255174195623272</v>
+        <v>6.09483531170162</v>
       </c>
       <c r="E9" t="n">
-        <v>14.73407727787267</v>
+        <v>14.75771202472437</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.688243915649621</v>
+        <v>2.22433724280165</v>
       </c>
       <c r="C10" t="n">
-        <v>8.60037027919876</v>
+        <v>8.301805599176408</v>
       </c>
       <c r="D10" t="n">
-        <v>6.809985961476492</v>
+        <v>6.519201035570637</v>
       </c>
       <c r="E10" t="n">
-        <v>17.09860015632487</v>
+        <v>17.0453438775487</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.973783709944456</v>
+        <v>2.657662569971706</v>
       </c>
       <c r="C11" t="n">
-        <v>10.24420338264728</v>
+        <v>9.86695809114217</v>
       </c>
       <c r="D11" t="n">
-        <v>7.386207890842336</v>
+        <v>7.008709490331315</v>
       </c>
       <c r="E11" t="n">
-        <v>19.60419498343408</v>
+        <v>19.53333015144519</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.258678148058155</v>
+        <v>3.0879385964245</v>
       </c>
       <c r="C12" t="n">
-        <v>11.98482855300858</v>
+        <v>11.47105898585206</v>
       </c>
       <c r="D12" t="n">
-        <v>8.002876684664541</v>
+        <v>7.452057294325129</v>
       </c>
       <c r="E12" t="n">
-        <v>22.24638338573128</v>
+        <v>22.01105487660168</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.524983298999787</v>
+        <v>3.487434079413033</v>
       </c>
       <c r="C13" t="n">
-        <v>13.72793790798241</v>
+        <v>13.08633952113328</v>
       </c>
       <c r="D13" t="n">
-        <v>8.529083963427944</v>
+        <v>7.843895628873617</v>
       </c>
       <c r="E13" t="n">
-        <v>24.78200517041014</v>
+        <v>24.41766922941993</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.457846253421301</v>
+        <v>1.993379808610894</v>
       </c>
       <c r="C14" t="n">
-        <v>9.583585469408343</v>
+        <v>9.133513051873436</v>
       </c>
       <c r="D14" t="n">
-        <v>6.530644633512036</v>
+        <v>5.953985666991546</v>
       </c>
       <c r="E14" t="n">
-        <v>17.57207635634168</v>
+        <v>17.08087852747587</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.471580903803714</v>
+        <v>2.062111965385213</v>
       </c>
       <c r="C15" t="n">
-        <v>10.37739721063119</v>
+        <v>9.832468329911952</v>
       </c>
       <c r="D15" t="n">
-        <v>6.588616835447811</v>
+        <v>5.925573888430644</v>
       </c>
       <c r="E15" t="n">
-        <v>18.43759494988271</v>
+        <v>17.82015418372781</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.686102594658685</v>
+        <v>2.405065890909751</v>
       </c>
       <c r="C16" t="n">
-        <v>12.29934505628108</v>
+        <v>11.57923311521605</v>
       </c>
       <c r="D16" t="n">
-        <v>7.073767098455458</v>
+        <v>6.323152256219474</v>
       </c>
       <c r="E16" t="n">
-        <v>21.05921474939523</v>
+        <v>20.30745126234527</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.342530168080471</v>
+        <v>1.937282744790231</v>
       </c>
       <c r="C17" t="n">
-        <v>11.33671197983596</v>
+        <v>10.61386096267608</v>
       </c>
       <c r="D17" t="n">
-        <v>6.589470955950507</v>
+        <v>5.826397735347631</v>
       </c>
       <c r="E17" t="n">
-        <v>19.26871310386694</v>
+        <v>18.37754144281394</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.51428692893845</v>
+        <v>2.219005066000896</v>
       </c>
       <c r="C18" t="n">
-        <v>13.26753482473225</v>
+        <v>12.36555412145549</v>
       </c>
       <c r="D18" t="n">
-        <v>7.080688419770398</v>
+        <v>6.217270766316456</v>
       </c>
       <c r="E18" t="n">
-        <v>21.86251017344109</v>
+        <v>20.80182995377284</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.502466686579319</v>
+        <v>2.233603654363046</v>
       </c>
       <c r="C19" t="n">
-        <v>14.20194265468028</v>
+        <v>13.19758530080466</v>
       </c>
       <c r="D19" t="n">
-        <v>7.203789764405906</v>
+        <v>6.276627232515218</v>
       </c>
       <c r="E19" t="n">
-        <v>22.9081991056655</v>
+        <v>21.70781618768292</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.651466535652857</v>
+        <v>2.493590081401686</v>
       </c>
       <c r="C20" t="n">
-        <v>16.33576147238367</v>
+        <v>15.16088435975743</v>
       </c>
       <c r="D20" t="n">
-        <v>7.695066133088052</v>
+        <v>6.662022111294346</v>
       </c>
       <c r="E20" t="n">
-        <v>25.68229414112458</v>
+        <v>24.31649655245346</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9718026000027903</v>
+        <v>1.483136074282699</v>
       </c>
       <c r="C21" t="n">
-        <v>12.05452663127306</v>
+        <v>11.16014465522717</v>
       </c>
       <c r="D21" t="n">
-        <v>6.455069695239119</v>
+        <v>5.539069634745718</v>
       </c>
       <c r="E21" t="n">
-        <v>19.48139892651497</v>
+        <v>18.18235036425559</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_96_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.294725372641775</v>
+        <v>2.619096229796128</v>
       </c>
       <c r="C3" t="n">
-        <v>4.640521994250872</v>
+        <v>7.653515739600832</v>
       </c>
       <c r="D3" t="n">
-        <v>6.041650922176904</v>
+        <v>8.251862148609053</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97689828906955</v>
+        <v>18.52447411800601</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.480958237887168</v>
+        <v>1.136998521982256</v>
       </c>
       <c r="C4" t="n">
-        <v>5.176794278670436</v>
+        <v>4.433695887424579</v>
       </c>
       <c r="D4" t="n">
-        <v>6.328822331314694</v>
+        <v>5.917660817653471</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9865748478723</v>
+        <v>11.48835522706031</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.717643692008971</v>
+        <v>1.288590791067694</v>
       </c>
       <c r="C5" t="n">
-        <v>5.873719255207845</v>
+        <v>5.031418739973259</v>
       </c>
       <c r="D5" t="n">
-        <v>6.58427440991431</v>
+        <v>6.301582427759527</v>
       </c>
       <c r="E5" t="n">
-        <v>14.17563735713113</v>
+        <v>12.62159195880048</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.972914935116205</v>
+        <v>1.449002436846609</v>
       </c>
       <c r="C6" t="n">
-        <v>6.766516756202575</v>
+        <v>5.800963205709597</v>
       </c>
       <c r="D6" t="n">
-        <v>7.01727602271855</v>
+        <v>6.731551408328708</v>
       </c>
       <c r="E6" t="n">
-        <v>15.75670771403733</v>
+        <v>13.98151705088491</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.248785523190296</v>
+        <v>1.607687521055875</v>
       </c>
       <c r="C7" t="n">
-        <v>7.83521365991368</v>
+        <v>6.733906213877408</v>
       </c>
       <c r="D7" t="n">
-        <v>7.36979156099785</v>
+        <v>7.158533688240326</v>
       </c>
       <c r="E7" t="n">
-        <v>17.45379074410183</v>
+        <v>15.50012742317361</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.4181943246907</v>
+        <v>1.765120744143879</v>
       </c>
       <c r="C8" t="n">
-        <v>5.537105621331631</v>
+        <v>7.809309848078954</v>
       </c>
       <c r="D8" t="n">
-        <v>5.639472283426862</v>
+        <v>7.558160734923427</v>
       </c>
       <c r="E8" t="n">
-        <v>12.59477222944919</v>
+        <v>17.13259132714626</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.808465363958386</v>
+        <v>1.911394183014578</v>
       </c>
       <c r="C9" t="n">
-        <v>6.854411349064364</v>
+        <v>9.004372896695815</v>
       </c>
       <c r="D9" t="n">
-        <v>6.09483531170162</v>
+        <v>8.076266041482533</v>
       </c>
       <c r="E9" t="n">
-        <v>14.75771202472437</v>
+        <v>18.99203312119293</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.22433724280165</v>
+        <v>1.168260133099619</v>
       </c>
       <c r="C10" t="n">
-        <v>8.301805599176408</v>
+        <v>6.670298244441146</v>
       </c>
       <c r="D10" t="n">
-        <v>6.519201035570637</v>
+        <v>6.356404050962313</v>
       </c>
       <c r="E10" t="n">
-        <v>17.0453438775487</v>
+        <v>14.19496242850308</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.657662569971706</v>
+        <v>1.103808396315816</v>
       </c>
       <c r="C11" t="n">
-        <v>9.86695809114217</v>
+        <v>7.072893342998679</v>
       </c>
       <c r="D11" t="n">
-        <v>7.008709490331315</v>
+        <v>6.256697754119008</v>
       </c>
       <c r="E11" t="n">
-        <v>19.53333015144519</v>
+        <v>14.4333994934335</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.0879385964245</v>
+        <v>1.1957883387267</v>
       </c>
       <c r="C12" t="n">
-        <v>11.47105898585206</v>
+        <v>8.354113366948935</v>
       </c>
       <c r="D12" t="n">
-        <v>7.452057294325129</v>
+        <v>6.684720118216531</v>
       </c>
       <c r="E12" t="n">
-        <v>22.01105487660168</v>
+        <v>16.23462182389217</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.487434079413033</v>
+        <v>0.9395031005330702</v>
       </c>
       <c r="C13" t="n">
-        <v>13.08633952113328</v>
+        <v>7.959764949107077</v>
       </c>
       <c r="D13" t="n">
-        <v>7.843895628873617</v>
+        <v>6.144807968265999</v>
       </c>
       <c r="E13" t="n">
-        <v>24.41766922941993</v>
+        <v>15.04407601790615</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.993379808610894</v>
+        <v>1.022608043697563</v>
       </c>
       <c r="C14" t="n">
-        <v>9.133513051873436</v>
+        <v>9.336263587754488</v>
       </c>
       <c r="D14" t="n">
-        <v>5.953985666991546</v>
+        <v>6.543613520685138</v>
       </c>
       <c r="E14" t="n">
-        <v>17.08087852747587</v>
+        <v>16.90248515213719</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.062111965385213</v>
+        <v>0.9966408169202347</v>
       </c>
       <c r="C15" t="n">
-        <v>9.832468329911952</v>
+        <v>10.10732823466993</v>
       </c>
       <c r="D15" t="n">
-        <v>5.925573888430644</v>
+        <v>6.629948413796602</v>
       </c>
       <c r="E15" t="n">
-        <v>17.82015418372781</v>
+        <v>17.73391746538677</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.405065890909751</v>
+        <v>1.09252811519402</v>
       </c>
       <c r="C16" t="n">
-        <v>11.57923311521605</v>
+        <v>11.87001696773691</v>
       </c>
       <c r="D16" t="n">
-        <v>6.323152256219474</v>
+        <v>7.047132283239243</v>
       </c>
       <c r="E16" t="n">
-        <v>20.30745126234527</v>
+        <v>20.00967736617017</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.937282744790231</v>
+        <v>0.6558663712991242</v>
       </c>
       <c r="C17" t="n">
-        <v>10.61386096267608</v>
+        <v>8.984631012524408</v>
       </c>
       <c r="D17" t="n">
-        <v>5.826397735347631</v>
+        <v>5.863193639302802</v>
       </c>
       <c r="E17" t="n">
-        <v>18.37754144281394</v>
+        <v>15.50369102312633</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.219005066000896</v>
+        <v>0.5160164108291661</v>
       </c>
       <c r="C18" t="n">
-        <v>12.36555412145549</v>
+        <v>8.112191097668438</v>
       </c>
       <c r="D18" t="n">
-        <v>6.217270766316456</v>
+        <v>5.348767659754516</v>
       </c>
       <c r="E18" t="n">
-        <v>20.80182995377284</v>
+        <v>13.97697516825212</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.233603654363046</v>
+        <v>0.6030483448106458</v>
       </c>
       <c r="C19" t="n">
-        <v>13.19758530080466</v>
+        <v>10.09465387180811</v>
       </c>
       <c r="D19" t="n">
-        <v>6.276627232515218</v>
+        <v>5.881454146601793</v>
       </c>
       <c r="E19" t="n">
-        <v>21.70781618768292</v>
+        <v>16.57915636322054</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.493590081401686</v>
+        <v>0.6844843168779187</v>
       </c>
       <c r="C20" t="n">
-        <v>15.16088435975743</v>
+        <v>12.17117789349166</v>
       </c>
       <c r="D20" t="n">
-        <v>6.662022111294346</v>
+        <v>6.427737839152887</v>
       </c>
       <c r="E20" t="n">
-        <v>24.31649655245346</v>
+        <v>19.28340004952247</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.483136074282699</v>
+        <v>0.7584491889158734</v>
       </c>
       <c r="C21" t="n">
-        <v>11.16014465522717</v>
+        <v>14.21679649744553</v>
       </c>
       <c r="D21" t="n">
-        <v>5.539069634745718</v>
+        <v>7.006301396219617</v>
       </c>
       <c r="E21" t="n">
-        <v>18.18235036425559</v>
+        <v>21.98154708258102</v>
       </c>
     </row>
   </sheetData>
